--- a/docs/table_definition.xlsx
+++ b/docs/table_definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\educure\ryuta-nakagawa-educure-app\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA72909-449B-4B5A-B043-9206CF74DF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288E70EF-2142-49F3-874A-691EF5BEB966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D521E484-343C-4318-A4C2-8A5E477361C4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="66">
   <si>
     <t>テーブル定義書</t>
     <rPh sb="4" eb="7">
@@ -1185,7 +1185,9 @@
       <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2">
+        <v>3</v>
+      </c>
       <c r="B18" s="2"/>
       <c r="C18" s="4" t="s">
         <v>40</v>
@@ -1211,7 +1213,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1238,7 +1240,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1557,9 +1559,7 @@
       <c r="H33" s="2">
         <v>8</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="I33" s="4"/>
       <c r="J33" s="4" t="s">
         <v>32</v>
       </c>
